--- a/1-Processing/Protocol01/Multi/Results/HT_Contributions_Summary.xlsx
+++ b/1-Processing/Protocol01/Multi/Results/HT_Contributions_Summary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="92" uniqueCount="22">
   <si>
     <t>PatientID</t>
   </si>
@@ -21,10 +21,16 @@
     <t>18792</t>
   </si>
   <si>
+    <t>30432</t>
+  </si>
+  <si>
     <t>Side</t>
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>R</t>
   </si>
   <si>
     <t>Task</t>
@@ -118,26 +124,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="true"/>
     <col min="2" max="2" width="4.59765625" customWidth="true"/>
-    <col min="3" max="3" width="4.796875" customWidth="true"/>
+    <col min="3" max="3" width="10" customWidth="true"/>
     <col min="4" max="4" width="11.19921875" customWidth="true"/>
-    <col min="5" max="5" width="11.46484375" customWidth="true"/>
-    <col min="6" max="6" width="11.06640625" customWidth="true"/>
-    <col min="7" max="7" width="10.86328125" customWidth="true"/>
-    <col min="8" max="8" width="10.46484375" customWidth="true"/>
-    <col min="9" max="9" width="11" customWidth="true"/>
-    <col min="10" max="10" width="10.59765625" customWidth="true"/>
+    <col min="5" max="5" width="11.796875" customWidth="true"/>
+    <col min="6" max="6" width="11.796875" customWidth="true"/>
+    <col min="7" max="7" width="11.796875" customWidth="true"/>
+    <col min="8" max="8" width="11.796875" customWidth="true"/>
+    <col min="9" max="9" width="11.796875" customWidth="true"/>
+    <col min="10" max="10" width="11.796875" customWidth="true"/>
     <col min="11" max="11" width="12.265625" customWidth="true"/>
     <col min="12" max="12" width="12.53125" customWidth="true"/>
     <col min="13" max="13" width="12.1328125" customWidth="true"/>
     <col min="14" max="14" width="11.9296875" customWidth="true"/>
-    <col min="15" max="15" width="11.53125" customWidth="true"/>
+    <col min="15" max="15" width="11.796875" customWidth="true"/>
     <col min="16" max="16" width="12.06640625" customWidth="true"/>
-    <col min="17" max="17" width="11.6640625" customWidth="true"/>
+    <col min="17" max="17" width="11.796875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -145,52 +151,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -198,10 +204,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="0">
         <v>39.524454600576526</v>
@@ -244,6 +250,59 @@
       </c>
       <c r="Q2" s="0">
         <v>3.4954069293771455</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="0">
+        <v>135.5289771159544</v>
+      </c>
+      <c r="E3" s="0">
+        <v>97.574198154681326</v>
+      </c>
+      <c r="F3" s="0">
+        <v>71.995081960369163</v>
+      </c>
+      <c r="G3" s="0">
+        <v>23.829512057307074</v>
+      </c>
+      <c r="H3" s="0">
+        <v>17.582595666548329</v>
+      </c>
+      <c r="I3" s="0">
+        <v>11.958301354285114</v>
+      </c>
+      <c r="J3" s="0">
+        <v>8.8234277338741816</v>
+      </c>
+      <c r="K3" s="0">
+        <v>140.91229681029918</v>
+      </c>
+      <c r="L3" s="0">
+        <v>78.101728571196702</v>
+      </c>
+      <c r="M3" s="0">
+        <v>55.425772156946564</v>
+      </c>
+      <c r="N3" s="0">
+        <v>48.877344863491373</v>
+      </c>
+      <c r="O3" s="0">
+        <v>34.686358798971021</v>
+      </c>
+      <c r="P3" s="0">
+        <v>14.740195286235709</v>
+      </c>
+      <c r="Q3" s="0">
+        <v>10.460545757819455</v>
       </c>
     </row>
   </sheetData>
